--- a/output/pdf_financials_xlsx/NUKE.xlsx
+++ b/output/pdf_financials_xlsx/NUKE.xlsx
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.15473</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.129625</v>
       </c>
     </row>
     <row r="35">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.15473</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.129625</v>
       </c>
     </row>
     <row r="37">
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.183585</v>
+        <v>0.028855</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.138091</v>
+        <v>0.008466</v>
       </c>
     </row>
     <row r="49">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
